--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_03.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_03.xlsx
@@ -480,25 +480,25 @@
         <v>45717</v>
       </c>
       <c r="B5" t="n">
-        <v>1376.68</v>
+        <v>1511.99</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>992.62</v>
+        <v>1097.68</v>
       </c>
       <c r="E5" t="n">
-        <v>273.44</v>
+        <v>296.91</v>
       </c>
       <c r="F5" t="n">
-        <v>1874</v>
+        <v>1489</v>
       </c>
       <c r="G5" t="n">
-        <v>360085</v>
+        <v>408842</v>
       </c>
       <c r="H5" t="n">
-        <v>64981</v>
+        <v>68754</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45718</v>
       </c>
       <c r="B6" t="n">
-        <v>1340.65</v>
+        <v>1332.39</v>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>21.16</v>
       </c>
       <c r="D6" t="n">
-        <v>972.86</v>
+        <v>969.36</v>
       </c>
       <c r="E6" t="n">
-        <v>266.02</v>
+        <v>267.16</v>
       </c>
       <c r="F6" t="n">
-        <v>1866</v>
+        <v>1336</v>
       </c>
       <c r="G6" t="n">
-        <v>374552</v>
+        <v>348383</v>
       </c>
       <c r="H6" t="n">
-        <v>59834</v>
+        <v>66365</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45719</v>
       </c>
       <c r="B7" t="n">
-        <v>1493.09</v>
+        <v>1429.4</v>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>23.07</v>
       </c>
       <c r="D7" t="n">
-        <v>1089.3</v>
+        <v>1037.49</v>
       </c>
       <c r="E7" t="n">
-        <v>294.1</v>
+        <v>283.05</v>
       </c>
       <c r="F7" t="n">
-        <v>2233</v>
+        <v>1311</v>
       </c>
       <c r="G7" t="n">
-        <v>405339</v>
+        <v>377749</v>
       </c>
       <c r="H7" t="n">
-        <v>67159</v>
+        <v>70010</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45720</v>
       </c>
       <c r="B8" t="n">
-        <v>1486.66</v>
+        <v>1350.04</v>
       </c>
       <c r="C8" t="n">
-        <v>23.24</v>
+        <v>22.01</v>
       </c>
       <c r="D8" t="n">
-        <v>1070.95</v>
+        <v>983.29</v>
       </c>
       <c r="E8" t="n">
-        <v>301.74</v>
+        <v>259.46</v>
       </c>
       <c r="F8" t="n">
-        <v>2199</v>
+        <v>1222</v>
       </c>
       <c r="G8" t="n">
-        <v>386643</v>
+        <v>360013</v>
       </c>
       <c r="H8" t="n">
-        <v>66903</v>
+        <v>59959</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45721</v>
       </c>
       <c r="B9" t="n">
-        <v>1480.62</v>
+        <v>1470.78</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>1069.73</v>
+        <v>1073.63</v>
       </c>
       <c r="E9" t="n">
-        <v>291.66</v>
+        <v>290.69</v>
       </c>
       <c r="F9" t="n">
-        <v>2245</v>
+        <v>1564</v>
       </c>
       <c r="G9" t="n">
-        <v>364922</v>
+        <v>374805</v>
       </c>
       <c r="H9" t="n">
-        <v>63687</v>
+        <v>69396</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45722</v>
       </c>
       <c r="B10" t="n">
-        <v>1426.36</v>
+        <v>1500.96</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>23.6</v>
       </c>
       <c r="D10" t="n">
-        <v>1038.13</v>
+        <v>1095.38</v>
       </c>
       <c r="E10" t="n">
-        <v>280.84</v>
+        <v>298.17</v>
       </c>
       <c r="F10" t="n">
-        <v>1878</v>
+        <v>1552</v>
       </c>
       <c r="G10" t="n">
-        <v>356236</v>
+        <v>386707</v>
       </c>
       <c r="H10" t="n">
-        <v>67503</v>
+        <v>65361</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45723</v>
       </c>
       <c r="B11" t="n">
-        <v>1487.21</v>
+        <v>1413.73</v>
       </c>
       <c r="C11" t="n">
-        <v>23.06</v>
+        <v>22.49</v>
       </c>
       <c r="D11" t="n">
-        <v>1081.76</v>
+        <v>1026.48</v>
       </c>
       <c r="E11" t="n">
-        <v>294.74</v>
+        <v>283.05</v>
       </c>
       <c r="F11" t="n">
-        <v>2513</v>
+        <v>1285</v>
       </c>
       <c r="G11" t="n">
-        <v>369480</v>
+        <v>379402</v>
       </c>
       <c r="H11" t="n">
-        <v>65656</v>
+        <v>62791</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45724</v>
       </c>
       <c r="B12" t="n">
-        <v>1480.48</v>
+        <v>1480.67</v>
       </c>
       <c r="C12" t="n">
-        <v>23.45</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>1080.85</v>
+        <v>1071.4</v>
       </c>
       <c r="E12" t="n">
-        <v>303.24</v>
+        <v>287.09</v>
       </c>
       <c r="F12" t="n">
-        <v>2339</v>
+        <v>1420</v>
       </c>
       <c r="G12" t="n">
-        <v>398962</v>
+        <v>400429</v>
       </c>
       <c r="H12" t="n">
-        <v>67351</v>
+        <v>73173</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45725</v>
       </c>
       <c r="B13" t="n">
-        <v>1400.98</v>
+        <v>1501.48</v>
       </c>
       <c r="C13" t="n">
-        <v>22.53</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>1022.77</v>
+        <v>1092.96</v>
       </c>
       <c r="E13" t="n">
-        <v>282.2</v>
+        <v>294.28</v>
       </c>
       <c r="F13" t="n">
-        <v>1828</v>
+        <v>1314</v>
       </c>
       <c r="G13" t="n">
-        <v>382513</v>
+        <v>398064</v>
       </c>
       <c r="H13" t="n">
-        <v>66065</v>
+        <v>73323</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45726</v>
       </c>
       <c r="B14" t="n">
-        <v>1513.69</v>
+        <v>1368.04</v>
       </c>
       <c r="C14" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>1094.38</v>
+        <v>986.22</v>
       </c>
       <c r="E14" t="n">
-        <v>297.01</v>
+        <v>274.61</v>
       </c>
       <c r="F14" t="n">
-        <v>2368</v>
+        <v>1243</v>
       </c>
       <c r="G14" t="n">
-        <v>388407</v>
+        <v>373249</v>
       </c>
       <c r="H14" t="n">
-        <v>66843</v>
+        <v>61269</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45727</v>
       </c>
       <c r="B15" t="n">
-        <v>1565.7</v>
+        <v>1608</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>1137.01</v>
+        <v>1154.07</v>
       </c>
       <c r="E15" t="n">
-        <v>306.39</v>
+        <v>325.69</v>
       </c>
       <c r="F15" t="n">
-        <v>2158</v>
+        <v>1504</v>
       </c>
       <c r="G15" t="n">
-        <v>398118</v>
+        <v>415784</v>
       </c>
       <c r="H15" t="n">
-        <v>71359</v>
+        <v>72336</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45728</v>
       </c>
       <c r="B16" t="n">
-        <v>1517.01</v>
+        <v>1488.66</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>1104.76</v>
+        <v>1062.89</v>
       </c>
       <c r="E16" t="n">
-        <v>305.54</v>
+        <v>289.34</v>
       </c>
       <c r="F16" t="n">
-        <v>2105</v>
+        <v>1098</v>
       </c>
       <c r="G16" t="n">
-        <v>382862</v>
+        <v>381251</v>
       </c>
       <c r="H16" t="n">
-        <v>65941</v>
+        <v>68299</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45729</v>
       </c>
       <c r="B17" t="n">
-        <v>1496.68</v>
+        <v>1608</v>
       </c>
       <c r="C17" t="n">
-        <v>23.56</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>1081.58</v>
+        <v>1164.3</v>
       </c>
       <c r="E17" t="n">
-        <v>291.99</v>
+        <v>321.19</v>
       </c>
       <c r="F17" t="n">
-        <v>2500</v>
+        <v>1345</v>
       </c>
       <c r="G17" t="n">
-        <v>401231</v>
+        <v>424896</v>
       </c>
       <c r="H17" t="n">
-        <v>68456</v>
+        <v>76228</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45730</v>
       </c>
       <c r="B18" t="n">
-        <v>1346.8</v>
+        <v>1542.27</v>
       </c>
       <c r="C18" t="n">
-        <v>21.87</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>985.98</v>
+        <v>1110.09</v>
       </c>
       <c r="E18" t="n">
-        <v>274.21</v>
+        <v>308.72</v>
       </c>
       <c r="F18" t="n">
-        <v>1900</v>
+        <v>1687</v>
       </c>
       <c r="G18" t="n">
-        <v>323745</v>
+        <v>379536</v>
       </c>
       <c r="H18" t="n">
-        <v>59166</v>
+        <v>67713</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45731</v>
       </c>
       <c r="B19" t="n">
-        <v>1383.71</v>
+        <v>1501.46</v>
       </c>
       <c r="C19" t="n">
-        <v>23.21</v>
+        <v>22.93</v>
       </c>
       <c r="D19" t="n">
-        <v>995.41</v>
+        <v>1093.84</v>
       </c>
       <c r="E19" t="n">
-        <v>269.95</v>
+        <v>302.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1797</v>
+        <v>1275</v>
       </c>
       <c r="G19" t="n">
-        <v>349414</v>
+        <v>385130</v>
       </c>
       <c r="H19" t="n">
-        <v>63099</v>
+        <v>67674</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45732</v>
       </c>
       <c r="B20" t="n">
-        <v>1159.44</v>
+        <v>1546.48</v>
       </c>
       <c r="C20" t="n">
-        <v>20.47</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>836.1</v>
+        <v>1122.78</v>
       </c>
       <c r="E20" t="n">
-        <v>226.1</v>
+        <v>310.66</v>
       </c>
       <c r="F20" t="n">
-        <v>1490</v>
+        <v>1283</v>
       </c>
       <c r="G20" t="n">
-        <v>356447</v>
+        <v>371755</v>
       </c>
       <c r="H20" t="n">
-        <v>52704</v>
+        <v>68721</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45733</v>
       </c>
       <c r="B21" t="n">
-        <v>1499.59</v>
+        <v>1470.92</v>
       </c>
       <c r="C21" t="n">
-        <v>23.56</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>1092.17</v>
+        <v>1068.94</v>
       </c>
       <c r="E21" t="n">
-        <v>298.32</v>
+        <v>294.45</v>
       </c>
       <c r="F21" t="n">
-        <v>2609</v>
+        <v>1232</v>
       </c>
       <c r="G21" t="n">
-        <v>382220</v>
+        <v>378738</v>
       </c>
       <c r="H21" t="n">
-        <v>71647</v>
+        <v>69791</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45734</v>
       </c>
       <c r="B22" t="n">
-        <v>1451.16</v>
+        <v>1494.27</v>
       </c>
       <c r="C22" t="n">
-        <v>23.52</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>1056.64</v>
+        <v>1089.12</v>
       </c>
       <c r="E22" t="n">
-        <v>288.74</v>
+        <v>304.08</v>
       </c>
       <c r="F22" t="n">
-        <v>2408</v>
+        <v>1371</v>
       </c>
       <c r="G22" t="n">
-        <v>380868</v>
+        <v>394567</v>
       </c>
       <c r="H22" t="n">
-        <v>67346</v>
+        <v>64068</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45735</v>
       </c>
       <c r="B23" t="n">
-        <v>1536.37</v>
+        <v>1458.96</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>1115.94</v>
+        <v>1062.28</v>
       </c>
       <c r="E23" t="n">
-        <v>310.42</v>
+        <v>294.03</v>
       </c>
       <c r="F23" t="n">
-        <v>2551</v>
+        <v>1849</v>
       </c>
       <c r="G23" t="n">
-        <v>393971</v>
+        <v>390797</v>
       </c>
       <c r="H23" t="n">
-        <v>69239</v>
+        <v>65915</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45736</v>
       </c>
       <c r="B24" t="n">
-        <v>1528.44</v>
+        <v>1440.54</v>
       </c>
       <c r="C24" t="n">
-        <v>22.81</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>1103.75</v>
+        <v>1047.74</v>
       </c>
       <c r="E24" t="n">
-        <v>305.13</v>
+        <v>285.59</v>
       </c>
       <c r="F24" t="n">
-        <v>2338</v>
+        <v>1281</v>
       </c>
       <c r="G24" t="n">
-        <v>379391</v>
+        <v>416611</v>
       </c>
       <c r="H24" t="n">
-        <v>63272</v>
+        <v>66047</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45737</v>
       </c>
       <c r="B25" t="n">
-        <v>1364.71</v>
+        <v>1422.64</v>
       </c>
       <c r="C25" t="n">
-        <v>21.88</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>991.83</v>
+        <v>1033.5</v>
       </c>
       <c r="E25" t="n">
-        <v>266.73</v>
+        <v>276.19</v>
       </c>
       <c r="F25" t="n">
-        <v>4960</v>
+        <v>1321</v>
       </c>
       <c r="G25" t="n">
-        <v>379786</v>
+        <v>397614</v>
       </c>
       <c r="H25" t="n">
-        <v>58127</v>
+        <v>67316</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45738</v>
       </c>
       <c r="B26" t="n">
-        <v>1524.25</v>
+        <v>1484.15</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>1101.5</v>
+        <v>1064.99</v>
       </c>
       <c r="E26" t="n">
-        <v>296.11</v>
+        <v>293.21</v>
       </c>
       <c r="F26" t="n">
-        <v>1923</v>
+        <v>1205</v>
       </c>
       <c r="G26" t="n">
-        <v>444370</v>
+        <v>379800</v>
       </c>
       <c r="H26" t="n">
-        <v>69186</v>
+        <v>71553</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45739</v>
       </c>
       <c r="B27" t="n">
-        <v>1378.13</v>
+        <v>1604</v>
       </c>
       <c r="C27" t="n">
-        <v>22.57</v>
+        <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>996.64</v>
+        <v>1162.55</v>
       </c>
       <c r="E27" t="n">
-        <v>271.42</v>
+        <v>319.58</v>
       </c>
       <c r="F27" t="n">
-        <v>2089</v>
+        <v>1551</v>
       </c>
       <c r="G27" t="n">
-        <v>361469</v>
+        <v>400687</v>
       </c>
       <c r="H27" t="n">
-        <v>60936</v>
+        <v>76193</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45740</v>
       </c>
       <c r="B28" t="n">
-        <v>1608</v>
+        <v>1555.12</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>1163.53</v>
+        <v>1124.14</v>
       </c>
       <c r="E28" t="n">
-        <v>331.32</v>
+        <v>306.32</v>
       </c>
       <c r="F28" t="n">
-        <v>2390</v>
+        <v>1481</v>
       </c>
       <c r="G28" t="n">
-        <v>408749</v>
+        <v>392296</v>
       </c>
       <c r="H28" t="n">
-        <v>77582</v>
+        <v>72943</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45741</v>
       </c>
       <c r="B29" t="n">
-        <v>1314.62</v>
+        <v>1543.28</v>
       </c>
       <c r="C29" t="n">
-        <v>22.69</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>955.58</v>
+        <v>1120.56</v>
       </c>
       <c r="E29" t="n">
-        <v>256.98</v>
+        <v>308.88</v>
       </c>
       <c r="F29" t="n">
-        <v>1869</v>
+        <v>1355</v>
       </c>
       <c r="G29" t="n">
-        <v>372875</v>
+        <v>408047</v>
       </c>
       <c r="H29" t="n">
-        <v>61871</v>
+        <v>69219</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45742</v>
       </c>
       <c r="B30" t="n">
-        <v>1482.57</v>
+        <v>1528.39</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>1077.91</v>
+        <v>1109.27</v>
       </c>
       <c r="E30" t="n">
-        <v>296.78</v>
+        <v>305.21</v>
       </c>
       <c r="F30" t="n">
-        <v>2234</v>
+        <v>1464</v>
       </c>
       <c r="G30" t="n">
-        <v>400618</v>
+        <v>395430</v>
       </c>
       <c r="H30" t="n">
-        <v>70309</v>
+        <v>62883</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45743</v>
       </c>
       <c r="B31" t="n">
-        <v>1538.98</v>
+        <v>1488.27</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>1123.16</v>
+        <v>1077.64</v>
       </c>
       <c r="E31" t="n">
-        <v>296.98</v>
+        <v>299.23</v>
       </c>
       <c r="F31" t="n">
-        <v>2184</v>
+        <v>1399</v>
       </c>
       <c r="G31" t="n">
-        <v>394391</v>
+        <v>388311</v>
       </c>
       <c r="H31" t="n">
-        <v>69379</v>
+        <v>71921</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45744</v>
       </c>
       <c r="B32" t="n">
-        <v>1468.5</v>
+        <v>1395.97</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>1075.37</v>
+        <v>1005.66</v>
       </c>
       <c r="E32" t="n">
-        <v>282.58</v>
+        <v>280.31</v>
       </c>
       <c r="F32" t="n">
-        <v>1907</v>
+        <v>1453</v>
       </c>
       <c r="G32" t="n">
-        <v>388797</v>
+        <v>355435</v>
       </c>
       <c r="H32" t="n">
-        <v>67735</v>
+        <v>62747</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45745</v>
       </c>
       <c r="B33" t="n">
-        <v>1326.54</v>
+        <v>1432.53</v>
       </c>
       <c r="C33" t="n">
-        <v>21.24</v>
+        <v>21.82</v>
       </c>
       <c r="D33" t="n">
-        <v>964.5599999999999</v>
+        <v>1047.37</v>
       </c>
       <c r="E33" t="n">
-        <v>257.06</v>
+        <v>284.41</v>
       </c>
       <c r="F33" t="n">
-        <v>1836</v>
+        <v>1637</v>
       </c>
       <c r="G33" t="n">
-        <v>357660</v>
+        <v>355509</v>
       </c>
       <c r="H33" t="n">
-        <v>60024</v>
+        <v>65864</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45746</v>
       </c>
       <c r="B34" t="n">
-        <v>1438.68</v>
+        <v>1446.82</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>1047.87</v>
+        <v>1052.4</v>
       </c>
       <c r="E34" t="n">
-        <v>282.21</v>
+        <v>290.36</v>
       </c>
       <c r="F34" t="n">
-        <v>2011</v>
+        <v>1341</v>
       </c>
       <c r="G34" t="n">
-        <v>388672</v>
+        <v>381472</v>
       </c>
       <c r="H34" t="n">
-        <v>62765</v>
+        <v>64061</v>
       </c>
     </row>
     <row r="35">
@@ -1260,25 +1260,25 @@
         <v>45747</v>
       </c>
       <c r="B35" t="n">
-        <v>585.02</v>
+        <v>578.6900000000001</v>
       </c>
       <c r="C35" t="n">
         <v>9.74</v>
       </c>
       <c r="D35" t="n">
-        <v>424.76</v>
+        <v>420.55</v>
       </c>
       <c r="E35" t="n">
-        <v>120.64</v>
+        <v>118.01</v>
       </c>
       <c r="F35" t="n">
-        <v>1118</v>
+        <v>758</v>
       </c>
       <c r="G35" t="n">
-        <v>168105</v>
+        <v>169200</v>
       </c>
       <c r="H35" t="n">
-        <v>27508</v>
+        <v>27216</v>
       </c>
     </row>
     <row r="37">
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>44001.32000000001</v>
+        <v>44998.9</v>
       </c>
       <c r="C37" t="n">
-        <v>708.2</v>
+        <v>718.8200000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>31945.4</v>
+        <v>32628.57</v>
       </c>
       <c r="E37" t="n">
-        <v>8720.589999999998</v>
+        <v>8952.129999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>67720</v>
+        <v>42626</v>
       </c>
       <c r="G37" t="n">
-        <v>11600898</v>
+        <v>11770509</v>
       </c>
       <c r="H37" t="n">
-        <v>1993633</v>
+        <v>2069109</v>
       </c>
     </row>
   </sheetData>

--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_03.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_03.xlsx
@@ -480,25 +480,25 @@
         <v>45717</v>
       </c>
       <c r="B5" t="n">
-        <v>1511.99</v>
+        <v>1386.46</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>23.77</v>
       </c>
       <c r="D5" t="n">
-        <v>1097.68</v>
+        <v>1004.75</v>
       </c>
       <c r="E5" t="n">
-        <v>296.91</v>
+        <v>270.45</v>
       </c>
       <c r="F5" t="n">
-        <v>1489</v>
+        <v>1237</v>
       </c>
       <c r="G5" t="n">
-        <v>408842</v>
+        <v>336994</v>
       </c>
       <c r="H5" t="n">
-        <v>68754</v>
+        <v>62120</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45718</v>
       </c>
       <c r="B6" t="n">
-        <v>1332.39</v>
+        <v>1570.77</v>
       </c>
       <c r="C6" t="n">
-        <v>21.16</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>969.36</v>
+        <v>1136.56</v>
       </c>
       <c r="E6" t="n">
-        <v>267.16</v>
+        <v>307.15</v>
       </c>
       <c r="F6" t="n">
-        <v>1336</v>
+        <v>1451</v>
       </c>
       <c r="G6" t="n">
-        <v>348383</v>
+        <v>393356</v>
       </c>
       <c r="H6" t="n">
-        <v>66365</v>
+        <v>69441</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45719</v>
       </c>
       <c r="B7" t="n">
-        <v>1429.4</v>
+        <v>1430.83</v>
       </c>
       <c r="C7" t="n">
-        <v>23.07</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1037.49</v>
+        <v>1044.61</v>
       </c>
       <c r="E7" t="n">
-        <v>283.05</v>
+        <v>282.45</v>
       </c>
       <c r="F7" t="n">
-        <v>1311</v>
+        <v>1489</v>
       </c>
       <c r="G7" t="n">
-        <v>377749</v>
+        <v>397731</v>
       </c>
       <c r="H7" t="n">
-        <v>70010</v>
+        <v>63210</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45720</v>
       </c>
       <c r="B8" t="n">
-        <v>1350.04</v>
+        <v>1491.51</v>
       </c>
       <c r="C8" t="n">
-        <v>22.01</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>983.29</v>
+        <v>1077.69</v>
       </c>
       <c r="E8" t="n">
-        <v>259.46</v>
+        <v>281.72</v>
       </c>
       <c r="F8" t="n">
-        <v>1222</v>
+        <v>1313</v>
       </c>
       <c r="G8" t="n">
-        <v>360013</v>
+        <v>379091</v>
       </c>
       <c r="H8" t="n">
-        <v>59959</v>
+        <v>65132</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45721</v>
       </c>
       <c r="B9" t="n">
-        <v>1470.78</v>
+        <v>1259.4</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>20.94</v>
       </c>
       <c r="D9" t="n">
-        <v>1073.63</v>
+        <v>909.51</v>
       </c>
       <c r="E9" t="n">
-        <v>290.69</v>
+        <v>249.01</v>
       </c>
       <c r="F9" t="n">
-        <v>1564</v>
+        <v>1101</v>
       </c>
       <c r="G9" t="n">
-        <v>374805</v>
+        <v>341181</v>
       </c>
       <c r="H9" t="n">
-        <v>69396</v>
+        <v>57163</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45722</v>
       </c>
       <c r="B10" t="n">
-        <v>1500.96</v>
+        <v>1410.55</v>
       </c>
       <c r="C10" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>1095.38</v>
+        <v>1020.31</v>
       </c>
       <c r="E10" t="n">
-        <v>298.17</v>
+        <v>280.73</v>
       </c>
       <c r="F10" t="n">
-        <v>1552</v>
+        <v>1180</v>
       </c>
       <c r="G10" t="n">
-        <v>386707</v>
+        <v>393808</v>
       </c>
       <c r="H10" t="n">
-        <v>65361</v>
+        <v>64178</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45723</v>
       </c>
       <c r="B11" t="n">
-        <v>1413.73</v>
+        <v>1506.99</v>
       </c>
       <c r="C11" t="n">
-        <v>22.49</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>1026.48</v>
+        <v>1102.51</v>
       </c>
       <c r="E11" t="n">
-        <v>283.05</v>
+        <v>302.16</v>
       </c>
       <c r="F11" t="n">
-        <v>1285</v>
+        <v>1364</v>
       </c>
       <c r="G11" t="n">
-        <v>379402</v>
+        <v>378349</v>
       </c>
       <c r="H11" t="n">
-        <v>62791</v>
+        <v>72504</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45724</v>
       </c>
       <c r="B12" t="n">
-        <v>1480.67</v>
+        <v>1555.02</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>1071.4</v>
+        <v>1122.1</v>
       </c>
       <c r="E12" t="n">
-        <v>287.09</v>
+        <v>302.59</v>
       </c>
       <c r="F12" t="n">
-        <v>1420</v>
+        <v>1065</v>
       </c>
       <c r="G12" t="n">
-        <v>400429</v>
+        <v>401326</v>
       </c>
       <c r="H12" t="n">
-        <v>73173</v>
+        <v>71377</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45725</v>
       </c>
       <c r="B13" t="n">
-        <v>1501.48</v>
+        <v>1590.69</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>1092.96</v>
+        <v>1154.91</v>
       </c>
       <c r="E13" t="n">
-        <v>294.28</v>
+        <v>323.28</v>
       </c>
       <c r="F13" t="n">
-        <v>1314</v>
+        <v>1367</v>
       </c>
       <c r="G13" t="n">
-        <v>398064</v>
+        <v>434298</v>
       </c>
       <c r="H13" t="n">
-        <v>73323</v>
+        <v>71121</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45726</v>
       </c>
       <c r="B14" t="n">
-        <v>1368.04</v>
+        <v>1479.43</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>986.22</v>
+        <v>1078.53</v>
       </c>
       <c r="E14" t="n">
-        <v>274.61</v>
+        <v>298.86</v>
       </c>
       <c r="F14" t="n">
-        <v>1243</v>
+        <v>1875</v>
       </c>
       <c r="G14" t="n">
-        <v>373249</v>
+        <v>403292</v>
       </c>
       <c r="H14" t="n">
-        <v>61269</v>
+        <v>69911</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45727</v>
       </c>
       <c r="B15" t="n">
-        <v>1608</v>
+        <v>1415.7</v>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>22.32</v>
       </c>
       <c r="D15" t="n">
-        <v>1154.07</v>
+        <v>1024.53</v>
       </c>
       <c r="E15" t="n">
-        <v>325.69</v>
+        <v>282.61</v>
       </c>
       <c r="F15" t="n">
-        <v>1504</v>
+        <v>1254</v>
       </c>
       <c r="G15" t="n">
-        <v>415784</v>
+        <v>391463</v>
       </c>
       <c r="H15" t="n">
-        <v>72336</v>
+        <v>63629</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45728</v>
       </c>
       <c r="B16" t="n">
-        <v>1488.66</v>
+        <v>1372.34</v>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>22.08</v>
       </c>
       <c r="D16" t="n">
-        <v>1062.89</v>
+        <v>996.4299999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>289.34</v>
+        <v>279.69</v>
       </c>
       <c r="F16" t="n">
-        <v>1098</v>
+        <v>2677</v>
       </c>
       <c r="G16" t="n">
-        <v>381251</v>
+        <v>373586</v>
       </c>
       <c r="H16" t="n">
-        <v>68299</v>
+        <v>62536</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45729</v>
       </c>
       <c r="B17" t="n">
-        <v>1608</v>
+        <v>1395.7</v>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>22.46</v>
       </c>
       <c r="D17" t="n">
-        <v>1164.3</v>
+        <v>1010.27</v>
       </c>
       <c r="E17" t="n">
-        <v>321.19</v>
+        <v>288</v>
       </c>
       <c r="F17" t="n">
-        <v>1345</v>
+        <v>1389</v>
       </c>
       <c r="G17" t="n">
-        <v>424896</v>
+        <v>360849</v>
       </c>
       <c r="H17" t="n">
-        <v>76228</v>
+        <v>61527</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45730</v>
       </c>
       <c r="B18" t="n">
-        <v>1542.27</v>
+        <v>1323.31</v>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>20.87</v>
       </c>
       <c r="D18" t="n">
-        <v>1110.09</v>
+        <v>962.51</v>
       </c>
       <c r="E18" t="n">
-        <v>308.72</v>
+        <v>266.3</v>
       </c>
       <c r="F18" t="n">
-        <v>1687</v>
+        <v>1043</v>
       </c>
       <c r="G18" t="n">
-        <v>379536</v>
+        <v>358659</v>
       </c>
       <c r="H18" t="n">
-        <v>67713</v>
+        <v>60087</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45731</v>
       </c>
       <c r="B19" t="n">
-        <v>1501.46</v>
+        <v>1453.67</v>
       </c>
       <c r="C19" t="n">
-        <v>22.93</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>1093.84</v>
+        <v>1039.02</v>
       </c>
       <c r="E19" t="n">
-        <v>302.2</v>
+        <v>284.45</v>
       </c>
       <c r="F19" t="n">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="G19" t="n">
-        <v>385130</v>
+        <v>392441</v>
       </c>
       <c r="H19" t="n">
-        <v>67674</v>
+        <v>68236</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45732</v>
       </c>
       <c r="B20" t="n">
-        <v>1546.48</v>
+        <v>1472.78</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>1122.78</v>
+        <v>1062.9</v>
       </c>
       <c r="E20" t="n">
-        <v>310.66</v>
+        <v>295.06</v>
       </c>
       <c r="F20" t="n">
-        <v>1283</v>
+        <v>1394</v>
       </c>
       <c r="G20" t="n">
-        <v>371755</v>
+        <v>398838</v>
       </c>
       <c r="H20" t="n">
-        <v>68721</v>
+        <v>67763</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45733</v>
       </c>
       <c r="B21" t="n">
-        <v>1470.92</v>
+        <v>1477.89</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>1068.94</v>
+        <v>1075.47</v>
       </c>
       <c r="E21" t="n">
-        <v>294.45</v>
+        <v>301.58</v>
       </c>
       <c r="F21" t="n">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="G21" t="n">
-        <v>378738</v>
+        <v>399082</v>
       </c>
       <c r="H21" t="n">
-        <v>69791</v>
+        <v>69057</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45734</v>
       </c>
       <c r="B22" t="n">
-        <v>1494.27</v>
+        <v>1503.18</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>1089.12</v>
+        <v>1094.63</v>
       </c>
       <c r="E22" t="n">
-        <v>304.08</v>
+        <v>307.19</v>
       </c>
       <c r="F22" t="n">
-        <v>1371</v>
+        <v>1523</v>
       </c>
       <c r="G22" t="n">
-        <v>394567</v>
+        <v>421314</v>
       </c>
       <c r="H22" t="n">
-        <v>64068</v>
+        <v>69847</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45735</v>
       </c>
       <c r="B23" t="n">
-        <v>1458.96</v>
+        <v>1416.67</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>1062.28</v>
+        <v>1030.51</v>
       </c>
       <c r="E23" t="n">
-        <v>294.03</v>
+        <v>290.58</v>
       </c>
       <c r="F23" t="n">
-        <v>1849</v>
+        <v>1247</v>
       </c>
       <c r="G23" t="n">
-        <v>390797</v>
+        <v>339906</v>
       </c>
       <c r="H23" t="n">
-        <v>65915</v>
+        <v>64230</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45736</v>
       </c>
       <c r="B24" t="n">
-        <v>1440.54</v>
+        <v>1407.93</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>1047.74</v>
+        <v>1018.08</v>
       </c>
       <c r="E24" t="n">
-        <v>285.59</v>
+        <v>280.79</v>
       </c>
       <c r="F24" t="n">
-        <v>1281</v>
+        <v>1548</v>
       </c>
       <c r="G24" t="n">
-        <v>416611</v>
+        <v>381509</v>
       </c>
       <c r="H24" t="n">
-        <v>66047</v>
+        <v>68891</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45737</v>
       </c>
       <c r="B25" t="n">
-        <v>1422.64</v>
+        <v>1497.92</v>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>23.72</v>
       </c>
       <c r="D25" t="n">
-        <v>1033.5</v>
+        <v>1085.3</v>
       </c>
       <c r="E25" t="n">
-        <v>276.19</v>
+        <v>290.73</v>
       </c>
       <c r="F25" t="n">
-        <v>1321</v>
+        <v>1278</v>
       </c>
       <c r="G25" t="n">
-        <v>397614</v>
+        <v>396265</v>
       </c>
       <c r="H25" t="n">
-        <v>67316</v>
+        <v>66421</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45738</v>
       </c>
       <c r="B26" t="n">
-        <v>1484.15</v>
+        <v>1544.33</v>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>23.61</v>
       </c>
       <c r="D26" t="n">
-        <v>1064.99</v>
+        <v>1114.89</v>
       </c>
       <c r="E26" t="n">
-        <v>293.21</v>
+        <v>307.94</v>
       </c>
       <c r="F26" t="n">
-        <v>1205</v>
+        <v>1752</v>
       </c>
       <c r="G26" t="n">
-        <v>379800</v>
+        <v>427412</v>
       </c>
       <c r="H26" t="n">
-        <v>71553</v>
+        <v>72743</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45739</v>
       </c>
       <c r="B27" t="n">
-        <v>1604</v>
+        <v>1408.38</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>1162.55</v>
+        <v>1008.19</v>
       </c>
       <c r="E27" t="n">
-        <v>319.58</v>
+        <v>277.22</v>
       </c>
       <c r="F27" t="n">
-        <v>1551</v>
+        <v>1465</v>
       </c>
       <c r="G27" t="n">
-        <v>400687</v>
+        <v>379299</v>
       </c>
       <c r="H27" t="n">
-        <v>76193</v>
+        <v>64536</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45740</v>
       </c>
       <c r="B28" t="n">
-        <v>1555.12</v>
+        <v>1465.04</v>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>23.87</v>
       </c>
       <c r="D28" t="n">
-        <v>1124.14</v>
+        <v>1056.76</v>
       </c>
       <c r="E28" t="n">
-        <v>306.32</v>
+        <v>294.72</v>
       </c>
       <c r="F28" t="n">
-        <v>1481</v>
+        <v>1060</v>
       </c>
       <c r="G28" t="n">
-        <v>392296</v>
+        <v>380268</v>
       </c>
       <c r="H28" t="n">
-        <v>72943</v>
+        <v>69398</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45741</v>
       </c>
       <c r="B29" t="n">
-        <v>1543.28</v>
+        <v>1438.96</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>1120.56</v>
+        <v>1051.12</v>
       </c>
       <c r="E29" t="n">
-        <v>308.88</v>
+        <v>285.37</v>
       </c>
       <c r="F29" t="n">
-        <v>1355</v>
+        <v>1344</v>
       </c>
       <c r="G29" t="n">
-        <v>408047</v>
+        <v>372450</v>
       </c>
       <c r="H29" t="n">
-        <v>69219</v>
+        <v>65229</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45742</v>
       </c>
       <c r="B30" t="n">
-        <v>1528.39</v>
+        <v>1494.21</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>1109.27</v>
+        <v>1083.97</v>
       </c>
       <c r="E30" t="n">
-        <v>305.21</v>
+        <v>305.35</v>
       </c>
       <c r="F30" t="n">
-        <v>1464</v>
+        <v>1514</v>
       </c>
       <c r="G30" t="n">
-        <v>395430</v>
+        <v>405961</v>
       </c>
       <c r="H30" t="n">
-        <v>62883</v>
+        <v>69282</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45743</v>
       </c>
       <c r="B31" t="n">
-        <v>1488.27</v>
+        <v>1363.14</v>
       </c>
       <c r="C31" t="n">
-        <v>24</v>
+        <v>22.18</v>
       </c>
       <c r="D31" t="n">
-        <v>1077.64</v>
+        <v>992.42</v>
       </c>
       <c r="E31" t="n">
-        <v>299.23</v>
+        <v>276.32</v>
       </c>
       <c r="F31" t="n">
-        <v>1399</v>
+        <v>1150</v>
       </c>
       <c r="G31" t="n">
-        <v>388311</v>
+        <v>365844</v>
       </c>
       <c r="H31" t="n">
-        <v>71921</v>
+        <v>57622</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45744</v>
       </c>
       <c r="B32" t="n">
-        <v>1395.97</v>
+        <v>1486.04</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>1005.66</v>
+        <v>1075.33</v>
       </c>
       <c r="E32" t="n">
-        <v>280.31</v>
+        <v>302.17</v>
       </c>
       <c r="F32" t="n">
-        <v>1453</v>
+        <v>1421</v>
       </c>
       <c r="G32" t="n">
-        <v>355435</v>
+        <v>363415</v>
       </c>
       <c r="H32" t="n">
-        <v>62747</v>
+        <v>67921</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45745</v>
       </c>
       <c r="B33" t="n">
-        <v>1432.53</v>
+        <v>1554.37</v>
       </c>
       <c r="C33" t="n">
-        <v>21.82</v>
+        <v>24</v>
       </c>
       <c r="D33" t="n">
-        <v>1047.37</v>
+        <v>1126.81</v>
       </c>
       <c r="E33" t="n">
-        <v>284.41</v>
+        <v>317.14</v>
       </c>
       <c r="F33" t="n">
-        <v>1637</v>
+        <v>1903</v>
       </c>
       <c r="G33" t="n">
-        <v>355509</v>
+        <v>409637</v>
       </c>
       <c r="H33" t="n">
-        <v>65864</v>
+        <v>73620</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45746</v>
       </c>
       <c r="B34" t="n">
-        <v>1446.82</v>
+        <v>1418.89</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>1052.4</v>
+        <v>1022.16</v>
       </c>
       <c r="E34" t="n">
-        <v>290.36</v>
+        <v>284.64</v>
       </c>
       <c r="F34" t="n">
-        <v>1341</v>
+        <v>1182</v>
       </c>
       <c r="G34" t="n">
-        <v>381472</v>
+        <v>352436</v>
       </c>
       <c r="H34" t="n">
-        <v>64061</v>
+        <v>66616</v>
       </c>
     </row>
     <row r="35">
@@ -1260,25 +1260,25 @@
         <v>45747</v>
       </c>
       <c r="B35" t="n">
-        <v>578.6900000000001</v>
+        <v>607.17</v>
       </c>
       <c r="C35" t="n">
         <v>9.74</v>
       </c>
       <c r="D35" t="n">
-        <v>420.55</v>
+        <v>439.53</v>
       </c>
       <c r="E35" t="n">
-        <v>118.01</v>
+        <v>124.68</v>
       </c>
       <c r="F35" t="n">
-        <v>758</v>
+        <v>551</v>
       </c>
       <c r="G35" t="n">
-        <v>169200</v>
+        <v>163260</v>
       </c>
       <c r="H35" t="n">
-        <v>27216</v>
+        <v>27536</v>
       </c>
     </row>
     <row r="37">
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>44998.9</v>
+        <v>44199.27</v>
       </c>
       <c r="C37" t="n">
-        <v>718.8200000000001</v>
+        <v>715.5599999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>32628.57</v>
+        <v>32022.31</v>
       </c>
       <c r="E37" t="n">
-        <v>8952.129999999999</v>
+        <v>8840.93</v>
       </c>
       <c r="F37" t="n">
-        <v>42626</v>
+        <v>42634</v>
       </c>
       <c r="G37" t="n">
-        <v>11770509</v>
+        <v>11693320</v>
       </c>
       <c r="H37" t="n">
-        <v>2069109</v>
+        <v>2022884</v>
       </c>
     </row>
   </sheetData>
